--- a/input-output/Template.xlsx
+++ b/input-output/Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\Scheduler\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\Scheduler\input-output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4534F60E-B550-404A-93EB-91E5A7DC2E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C100CD5-08E5-4AA6-B4E1-DA04CBFB0DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32295" yWindow="4815" windowWidth="28800" windowHeight="15885" firstSheet="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="edited" sheetId="1" r:id="rId1"/>
@@ -848,8 +848,8 @@
       <c r="E5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>19</v>
+      <c r="F5" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>22</v>
@@ -932,8 +932,12 @@
         <v>23</v>
       </c>
       <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="L6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>19</v>
+      </c>
       <c r="N6" s="5" t="s">
         <v>11</v>
       </c>
@@ -1188,8 +1192,8 @@
       <c r="E10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>19</v>
+      <c r="F10" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>19</v>
@@ -1479,12 +1483,6 @@
       </c>
       <c r="K14" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="N14" s="7" t="s">
         <v>19</v>
@@ -1774,7 +1772,6 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1827,7 +1824,6 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>

--- a/input-output/Template.xlsx
+++ b/input-output/Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\Scheduler\input-output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmeverly/dev/Scheduler/input-output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C100CD5-08E5-4AA6-B4E1-DA04CBFB0DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D4B175-4799-6545-A63B-3980D595EC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4520" yWindow="600" windowWidth="33880" windowHeight="21660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="edited" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="josh" sheetId="4" r:id="rId6"/>
     <sheet name="megan" sheetId="3" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="31">
   <si>
     <t>Day 1</t>
   </si>
@@ -230,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -276,6 +276,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -590,10 +601,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Y18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -618,1366 +629,965 @@
       <c r="W1" s="3"/>
       <c r="X1" s="3"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" t="s">
         <v>7</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" t="s">
         <v>1</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="S2" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" t="s">
         <v>3</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" t="s">
         <v>4</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="V2" t="s">
         <v>5</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="W2" t="s">
         <v>6</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="X2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T3" t="s">
+        <v>18</v>
+      </c>
+      <c r="U3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q4">
+        <v>2</v>
+      </c>
+      <c r="R4" t="s">
+        <v>18</v>
+      </c>
+      <c r="S4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T4" t="s">
+        <v>16</v>
+      </c>
+      <c r="U4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V4" t="s">
+        <v>18</v>
+      </c>
+      <c r="W4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q5">
+        <v>3</v>
+      </c>
+      <c r="R5" t="s">
+        <v>16</v>
+      </c>
+      <c r="S5" t="s">
+        <v>16</v>
+      </c>
+      <c r="T5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U5" t="s">
+        <v>18</v>
+      </c>
+      <c r="V5" t="s">
+        <v>10</v>
+      </c>
+      <c r="W5" t="s">
+        <v>10</v>
+      </c>
+      <c r="X5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q6">
+        <v>4</v>
+      </c>
+      <c r="R6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T6" t="s">
+        <v>18</v>
+      </c>
+      <c r="U6" t="s">
+        <v>18</v>
+      </c>
+      <c r="V6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W6" t="s">
+        <v>16</v>
+      </c>
+      <c r="X6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q7">
+        <v>5</v>
+      </c>
+      <c r="R7" t="s">
+        <v>18</v>
+      </c>
+      <c r="S7" t="s">
+        <v>18</v>
+      </c>
+      <c r="T7" t="s">
+        <v>16</v>
+      </c>
+      <c r="U7" t="s">
+        <v>16</v>
+      </c>
+      <c r="V7" t="s">
+        <v>18</v>
+      </c>
+      <c r="W7" t="s">
+        <v>18</v>
+      </c>
+      <c r="X7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q8">
+        <v>6</v>
+      </c>
+      <c r="R8" t="s">
+        <v>16</v>
+      </c>
+      <c r="S8" t="s">
+        <v>16</v>
+      </c>
+      <c r="T8" t="s">
+        <v>18</v>
+      </c>
+      <c r="U8" t="s">
+        <v>18</v>
+      </c>
+      <c r="V8" t="s">
+        <v>22</v>
+      </c>
+      <c r="W8" t="s">
+        <v>22</v>
+      </c>
+      <c r="X8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q9">
+        <v>7</v>
+      </c>
+      <c r="R9" t="s">
+        <v>16</v>
+      </c>
+      <c r="S9" t="s">
+        <v>16</v>
+      </c>
+      <c r="T9" t="s">
+        <v>18</v>
+      </c>
+      <c r="U9" t="s">
+        <v>18</v>
+      </c>
+      <c r="V9" t="s">
+        <v>16</v>
+      </c>
+      <c r="W9" t="s">
+        <v>16</v>
+      </c>
+      <c r="X9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q10">
+        <v>8</v>
+      </c>
+      <c r="R10" t="s">
+        <v>18</v>
+      </c>
+      <c r="S10" t="s">
+        <v>18</v>
+      </c>
+      <c r="T10" t="s">
+        <v>16</v>
+      </c>
+      <c r="U10" t="s">
+        <v>16</v>
+      </c>
+      <c r="V10" t="s">
+        <v>18</v>
+      </c>
+      <c r="W10" t="s">
+        <v>18</v>
+      </c>
+      <c r="X10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11">
+        <v>9</v>
+      </c>
+      <c r="J11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" t="s">
+        <v>12</v>
+      </c>
+      <c r="M11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q11">
+        <v>9</v>
+      </c>
+      <c r="R11" t="s">
+        <v>16</v>
+      </c>
+      <c r="S11" t="s">
+        <v>16</v>
+      </c>
+      <c r="T11" t="s">
+        <v>18</v>
+      </c>
+      <c r="U11" t="s">
+        <v>18</v>
+      </c>
+      <c r="V11" t="s">
+        <v>10</v>
+      </c>
+      <c r="W11" t="s">
+        <v>10</v>
+      </c>
+      <c r="X11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q12">
+        <v>10</v>
+      </c>
+      <c r="R12" t="s">
+        <v>16</v>
+      </c>
+      <c r="S12" t="s">
+        <v>16</v>
+      </c>
+      <c r="T12" t="s">
+        <v>18</v>
+      </c>
+      <c r="U12" t="s">
+        <v>18</v>
+      </c>
+      <c r="V12" t="s">
+        <v>16</v>
+      </c>
+      <c r="W12" t="s">
+        <v>16</v>
+      </c>
+      <c r="X12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A13">
         <v>11</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13">
         <v>11</v>
       </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="5" t="s">
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q13">
         <v>11</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>1</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="T3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="U3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="7" t="s">
+      <c r="R13" t="s">
+        <v>18</v>
+      </c>
+      <c r="S13" t="s">
+        <v>18</v>
+      </c>
+      <c r="T13" t="s">
+        <v>16</v>
+      </c>
+      <c r="U13" t="s">
+        <v>16</v>
+      </c>
+      <c r="V13" t="s">
+        <v>18</v>
+      </c>
+      <c r="W13" t="s">
+        <v>18</v>
+      </c>
+      <c r="X13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14">
+        <v>12</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="L14" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>2</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="T4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="U4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="V4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="W4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="X4" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="10" t="s">
+      <c r="M14" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14">
+        <v>12</v>
+      </c>
+      <c r="R14" t="s">
+        <v>16</v>
+      </c>
+      <c r="S14" t="s">
+        <v>16</v>
+      </c>
+      <c r="T14" t="s">
+        <v>18</v>
+      </c>
+      <c r="U14" t="s">
+        <v>18</v>
+      </c>
+      <c r="V14" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="W14" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="3">
-        <v>3</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>3</v>
-      </c>
-      <c r="R5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="S5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="U5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="V5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="W5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="X5" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>4</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="3">
-        <v>4</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>4</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="S6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="T6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="U6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="V6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="W6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="X6" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="3">
-        <v>5</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>5</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="S7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="T7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="U7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="V7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="W7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="X7" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="3">
-        <v>6</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>6</v>
-      </c>
-      <c r="R8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="S8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="T8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="V8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="W8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="X8" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="3">
-        <v>7</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="N9" s="1"/>
-      <c r="O9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>7</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="S9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="T9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="U9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="V9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="W9" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="X9" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>8</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="3">
-        <v>8</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>8</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="T10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="U10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="V10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="W10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="X10" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>9</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="3">
-        <v>9</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="7" t="s">
+      <c r="X14" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="N11" s="1"/>
-      <c r="O11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>9</v>
-      </c>
-      <c r="R11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="T11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="U11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="V11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="W11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="X11" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>10</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="3">
-        <v>10</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>10</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="S12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="T12" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="U12" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="V12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="W12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="X12" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" s="3">
-        <v>11</v>
-      </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>11</v>
-      </c>
-      <c r="R13" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="T13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="U13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="V13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="W13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="X13" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>12</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" s="3">
-        <v>12</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="P14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>12</v>
-      </c>
-      <c r="R14" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="S14" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="T14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="U14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="V14" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="W14" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="X14" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="3">
-        <v>13</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N15" s="1"/>
-      <c r="O15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>13</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="S15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="T15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="U15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="V15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="W15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="X15" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>14</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="3">
-        <v>14</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="P16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>14</v>
-      </c>
-      <c r="R16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="S16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="T16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="U16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="V16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="W16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="X16" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A15" s="17"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="18"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="18"/>
+      <c r="X15" s="18"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="18"/>
+      <c r="T16" s="18"/>
+      <c r="U16" s="18"/>
+      <c r="V16" s="18"/>
+      <c r="W16" s="18"/>
+      <c r="X16" s="18"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A17" s="19"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
+      <c r="U17" s="19"/>
+      <c r="V17" s="19"/>
+      <c r="W17" s="19"/>
+      <c r="X17" s="19"/>
       <c r="Y17" s="1"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="19"/>
+      <c r="X18" s="19"/>
       <c r="Y18" s="1"/>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2"/>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
-      <c r="Y25" s="2"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
-      <c r="Y26" s="2"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
-      <c r="Y27" s="2"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="2"/>
-      <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
-      <c r="Y28" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1987,9 +1597,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3548DBC-C44D-45AE-90A4-BCC8D2CB8A7B}">
   <dimension ref="A1:Y33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2016,7 +1626,7 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2091,7 +1701,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -2106,7 +1716,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -2121,7 +1731,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -2145,7 +1755,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -2160,7 +1770,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -2172,7 +1782,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -2196,7 +1806,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -2211,7 +1821,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -2223,7 +1833,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -2244,7 +1854,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -2259,7 +1869,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -2274,7 +1884,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -2298,7 +1908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -2316,7 +1926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -2340,7 +1950,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R19" s="2"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
@@ -2350,7 +1960,7 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R20" s="3"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
@@ -2360,7 +1970,7 @@
       <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
     </row>
-    <row r="21" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R21" s="3"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
@@ -2370,7 +1980,7 @@
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
     </row>
-    <row r="22" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R22" s="3"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
@@ -2380,7 +1990,7 @@
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
     </row>
-    <row r="23" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R23" s="3"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
@@ -2390,7 +2000,7 @@
       <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
     </row>
-    <row r="24" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R24" s="3"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
@@ -2400,7 +2010,7 @@
       <c r="X24" s="2"/>
       <c r="Y24" s="2"/>
     </row>
-    <row r="25" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R25" s="3"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
@@ -2410,7 +2020,7 @@
       <c r="X25" s="2"/>
       <c r="Y25" s="2"/>
     </row>
-    <row r="26" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R26" s="3"/>
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
@@ -2420,7 +2030,7 @@
       <c r="X26" s="2"/>
       <c r="Y26" s="2"/>
     </row>
-    <row r="27" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R27" s="3"/>
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
@@ -2430,7 +2040,7 @@
       <c r="X27" s="16"/>
       <c r="Y27" s="2"/>
     </row>
-    <row r="28" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R28" s="3"/>
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
@@ -2440,7 +2050,7 @@
       <c r="X28" s="2"/>
       <c r="Y28" s="2"/>
     </row>
-    <row r="29" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R29" s="3"/>
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
@@ -2450,7 +2060,7 @@
       <c r="X29" s="16"/>
       <c r="Y29" s="2"/>
     </row>
-    <row r="30" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R30" s="3"/>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
@@ -2460,7 +2070,7 @@
       <c r="X30" s="2"/>
       <c r="Y30" s="2"/>
     </row>
-    <row r="31" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R31" s="3"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
@@ -2470,7 +2080,7 @@
       <c r="X31" s="2"/>
       <c r="Y31" s="2"/>
     </row>
-    <row r="32" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R32" s="3"/>
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
@@ -2480,7 +2090,7 @@
       <c r="X32" s="2"/>
       <c r="Y32" s="2"/>
     </row>
-    <row r="33" spans="18:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R33" s="3"/>
       <c r="S33" s="2"/>
       <c r="T33" s="2"/>
@@ -2498,9 +2108,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F78D7C3F-1D92-48CF-AD63-0D1B9295AEB0}">
   <dimension ref="A1:X16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2526,7 +2136,7 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2598,7 +2208,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H3" s="3">
         <v>1</v>
       </c>
@@ -2624,7 +2234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H4" s="3">
         <v>2</v>
       </c>
@@ -2648,7 +2258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H5" s="3">
         <v>3</v>
       </c>
@@ -2672,7 +2282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H6" s="3">
         <v>4</v>
       </c>
@@ -2698,7 +2308,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H7" s="3">
         <v>5</v>
       </c>
@@ -2722,7 +2332,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H8" s="3">
         <v>6</v>
       </c>
@@ -2739,7 +2349,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H9" s="3">
         <v>7</v>
       </c>
@@ -2761,7 +2371,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H10" s="3">
         <v>8</v>
       </c>
@@ -2787,7 +2397,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H11" s="3">
         <v>9</v>
       </c>
@@ -2809,7 +2419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H12" s="3">
         <v>10</v>
       </c>
@@ -2835,7 +2445,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H13" s="3">
         <v>11</v>
       </c>
@@ -2855,7 +2465,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H14" s="3">
         <v>12</v>
       </c>
@@ -2870,7 +2480,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H15" s="3">
         <v>13</v>
       </c>
@@ -2892,7 +2502,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="H16" s="3">
         <v>14</v>
       </c>
@@ -2924,9 +2534,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F2FBCA7-991E-416E-BC76-F9FCE5A45B7A}">
   <dimension ref="A1:X16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2952,7 +2562,7 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3024,7 +2634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
@@ -3048,7 +2658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -3060,7 +2670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="H5" s="3">
         <v>3</v>
       </c>
@@ -3069,7 +2679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3096,7 +2706,7 @@
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
@@ -3120,7 +2730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>24</v>
       </c>
@@ -3132,7 +2742,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
@@ -3156,7 +2766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C10" s="6" t="s">
         <v>12</v>
       </c>
@@ -3171,7 +2781,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C11" s="6" t="s">
         <v>12</v>
       </c>
@@ -3195,7 +2805,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="H12" s="3">
         <v>10</v>
       </c>
@@ -3204,7 +2814,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="B13" s="13" t="s">
         <v>12</v>
       </c>
@@ -3231,7 +2841,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C14" s="6" t="s">
         <v>12</v>
       </c>
@@ -3246,7 +2856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C15" s="6" t="s">
         <v>12</v>
       </c>
@@ -3278,7 +2888,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>12</v>
       </c>
@@ -3299,9 +2909,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0D1574-9AE2-4E61-BB35-8F44B7587AFB}">
   <dimension ref="A1:Z21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3329,7 +2939,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -3405,7 +3015,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="3">
         <v>1</v>
@@ -3421,7 +3031,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="3">
         <v>2</v>
@@ -3446,7 +3056,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="3">
         <v>3</v>
@@ -3462,7 +3072,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="3">
         <v>4</v>
@@ -3475,7 +3085,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="3">
         <v>5</v>
@@ -3497,7 +3107,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="3">
         <v>6</v>
@@ -3513,7 +3123,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="3">
         <v>7</v>
@@ -3538,7 +3148,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="3">
         <v>8</v>
@@ -3554,7 +3164,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="3">
         <v>9</v>
@@ -3573,7 +3183,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="3">
         <v>10</v>
@@ -3589,7 +3199,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="3">
         <v>11</v>
@@ -3608,7 +3218,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="3">
         <v>12</v>
@@ -3624,7 +3234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="3">
         <v>13</v>
@@ -3649,7 +3259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="3">
         <v>14</v>
@@ -3665,7 +3275,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="26:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="26:26" x14ac:dyDescent="0.2">
       <c r="Z21" t="s">
         <v>29</v>
       </c>
@@ -3678,9 +3288,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CAB1BDA-EB5B-42E5-9D86-BCECB7D9A403}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3706,7 +3316,7 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3778,7 +3388,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="E3" t="s">
         <v>9</v>
       </c>
@@ -3808,7 +3418,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C4" s="7" t="s">
         <v>19</v>
       </c>
@@ -3851,7 +3461,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>19</v>
       </c>
@@ -3908,7 +3518,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>19</v>
       </c>
@@ -3941,7 +3551,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
         <v>9</v>
       </c>
@@ -3977,7 +3587,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="E8" s="7" t="s">
         <v>19</v>
       </c>
@@ -4028,7 +3638,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C9" s="7" t="s">
         <v>19</v>
       </c>
@@ -4078,7 +3688,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
@@ -4128,7 +3738,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>19</v>
       </c>
@@ -4181,7 +3791,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>19</v>
       </c>
@@ -4240,7 +3850,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
         <v>9</v>
       </c>
@@ -4287,7 +3897,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>25</v>
       </c>
@@ -4344,7 +3954,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C15" s="7" t="s">
         <v>19</v>
       </c>
@@ -4394,7 +4004,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C16" s="7" t="s">
         <v>19</v>
       </c>
@@ -4437,7 +4047,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
         <v>30</v>
       </c>
@@ -4450,9 +4060,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89ABF2E-060E-4D3E-8B41-BD140A622AA8}">
   <dimension ref="A1:X16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4478,7 +4088,7 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -4550,7 +4160,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -4562,7 +4172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
@@ -4586,7 +4196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C5" s="4" t="s">
         <v>20</v>
       </c>
@@ -4601,7 +4211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C6" s="4" t="s">
         <v>20</v>
       </c>
@@ -4625,7 +4235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>20</v>
       </c>
@@ -4637,7 +4247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C8" s="12" t="s">
         <v>20</v>
       </c>
@@ -4661,7 +4271,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -4673,7 +4283,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -4694,7 +4304,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="H11" s="3">
         <v>9</v>
       </c>
@@ -4703,7 +4313,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C12" s="4" t="s">
         <v>10</v>
       </c>
@@ -4727,7 +4337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
@@ -4739,7 +4349,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C14" s="4" t="s">
         <v>10</v>
       </c>
@@ -4763,7 +4373,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>10</v>
       </c>
@@ -4775,7 +4385,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="C16" s="4" t="s">
         <v>10</v>
       </c>
